--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\hi-er\routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\dev\hi-er\apps\site\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CA52A0-ED1B-4F58-BF2C-7E3078C0BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C50805C-8CF5-42C9-80F6-4CA496FD8DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4716" yWindow="3648" windowWidth="19860" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="3936" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Nominal Speed</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>Annual Cost Savings</t>
+  </si>
+  <si>
+    <t>(Optional) Alternative number that the participant puts on the nameplate that they would like to be searchable in the HI database.</t>
+  </si>
+  <si>
+    <t>Alternative Part Number</t>
   </si>
 </sst>
 </file>
@@ -300,7 +306,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,8 +368,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,8 +449,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDEEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -852,6 +871,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -944,7 +978,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1280,6 +1314,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="89">
@@ -1708,46 +1745,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AR9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.59765625" customWidth="1"/>
     <col min="3" max="3" width="20.09765625" style="84" customWidth="1"/>
     <col min="4" max="4" width="22.5" style="84" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="21"/>
-    <col min="8" max="8" width="13.3984375" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" customWidth="1"/>
-    <col min="12" max="12" width="34.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.3984375" customWidth="1"/>
-    <col min="15" max="15" width="18.3984375" customWidth="1"/>
-    <col min="16" max="16" width="14.8984375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11" style="28" customWidth="1"/>
-    <col min="18" max="19" width="11" style="29" customWidth="1"/>
-    <col min="20" max="20" width="11" style="29"/>
-    <col min="21" max="21" width="11" style="30" customWidth="1"/>
-    <col min="22" max="22" width="11" style="29"/>
-    <col min="23" max="23" width="11" style="28"/>
-    <col min="24" max="24" width="11" style="54"/>
-    <col min="25" max="25" width="11" style="53"/>
-    <col min="26" max="26" width="11" style="29"/>
-    <col min="27" max="27" width="11" style="30"/>
-    <col min="28" max="28" width="11" style="28"/>
-    <col min="29" max="30" width="11" style="29"/>
-    <col min="31" max="31" width="11" style="30"/>
-    <col min="32" max="32" width="11" style="28"/>
-    <col min="33" max="33" width="11" style="28" customWidth="1"/>
-    <col min="34" max="35" width="11" style="29" customWidth="1"/>
-    <col min="36" max="36" width="11" style="30" customWidth="1"/>
-    <col min="37" max="37" width="21.3984375" style="56" customWidth="1"/>
-    <col min="38" max="41" width="18.59765625" style="56" customWidth="1"/>
-    <col min="42" max="42" width="11" style="94"/>
-    <col min="43" max="43" width="11" style="95"/>
+    <col min="5" max="5" width="22.5" style="84" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="21"/>
+    <col min="9" max="9" width="13.3984375" customWidth="1"/>
+    <col min="11" max="11" width="11.59765625" customWidth="1"/>
+    <col min="13" max="13" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.3984375" customWidth="1"/>
+    <col min="16" max="16" width="18.3984375" customWidth="1"/>
+    <col min="17" max="17" width="14.8984375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11" style="28" customWidth="1"/>
+    <col min="19" max="20" width="11" style="29" customWidth="1"/>
+    <col min="21" max="21" width="11" style="29"/>
+    <col min="22" max="22" width="11" style="30" customWidth="1"/>
+    <col min="23" max="23" width="11" style="29"/>
+    <col min="24" max="24" width="11" style="28"/>
+    <col min="25" max="25" width="11" style="54"/>
+    <col min="26" max="26" width="11" style="53"/>
+    <col min="27" max="27" width="11" style="29"/>
+    <col min="28" max="28" width="11" style="30"/>
+    <col min="29" max="29" width="11" style="28"/>
+    <col min="30" max="31" width="11" style="29"/>
+    <col min="32" max="32" width="11" style="30"/>
+    <col min="33" max="33" width="11" style="28"/>
+    <col min="34" max="34" width="11" style="28" customWidth="1"/>
+    <col min="35" max="36" width="11" style="29" customWidth="1"/>
+    <col min="37" max="37" width="11" style="30" customWidth="1"/>
+    <col min="38" max="38" width="21.3984375" style="56" customWidth="1"/>
+    <col min="39" max="42" width="18.59765625" style="56" customWidth="1"/>
+    <col min="43" max="43" width="11" style="94"/>
+    <col min="44" max="44" width="11" style="95"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>49</v>
       </c>
@@ -1760,125 +1798,128 @@
       <c r="D1" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="81" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="I1" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="J1" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="K1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="L1" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="M1" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="N1" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="59" t="s">
+      <c r="O1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="62" t="s">
+      <c r="Q1" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="63" t="s">
+      <c r="R1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="S1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="64" t="s">
+      <c r="T1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="65" t="s">
+      <c r="U1" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="66" t="s">
+      <c r="V1" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="67" t="s">
+      <c r="W1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="68" t="s">
+      <c r="X1" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="69" t="s">
+      <c r="Y1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="70" t="s">
+      <c r="Z1" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="70" t="s">
+      <c r="AA1" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="71" t="s">
+      <c r="AB1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="72" t="s">
+      <c r="AC1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="AC1" s="73" t="s">
+      <c r="AD1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="73" t="s">
+      <c r="AE1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="74" t="s">
+      <c r="AF1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="78" t="s">
+      <c r="AG1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AG1" s="75" t="s">
+      <c r="AH1" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="AH1" s="76" t="s">
+      <c r="AI1" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="76" t="s">
+      <c r="AJ1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="77" t="s">
+      <c r="AK1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="79" t="s">
+      <c r="AL1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="31" t="s">
+      <c r="AM1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="AM1" s="87" t="s">
+      <c r="AN1" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="87" t="s">
+      <c r="AO1" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="AO1" s="87" t="s">
+      <c r="AP1" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="AP1" s="96" t="s">
+      <c r="AQ1" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="AQ1" s="97" t="s">
+      <c r="AR1" s="97" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="7" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>64</v>
       </c>
@@ -1891,69 +1932,69 @@
       <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="18"/>
+      <c r="I2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="23"/>
+      <c r="R2" s="22"/>
       <c r="S2" s="23"/>
       <c r="T2" s="23"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="32" t="s">
+      <c r="U2" s="23"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="114" t="s">
+      <c r="X2" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="115"/>
       <c r="Y2" s="115"/>
       <c r="Z2" s="115"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="120" t="s">
+      <c r="AA2" s="115"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" s="121"/>
       <c r="AD2" s="121"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="111" t="s">
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="122"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="AH2" s="112"/>
       <c r="AI2" s="112"/>
-      <c r="AJ2" s="113"/>
-      <c r="AK2" s="34" t="s">
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="113"/>
+      <c r="AL2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AL2" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AM2" s="88" t="s">
+      <c r="AM2" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AN2" s="88" t="s">
@@ -1962,173 +2003,179 @@
       <c r="AO2" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="AP2" s="98" t="s">
+      <c r="AP2" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="AQ2" s="99" t="s">
+      <c r="AQ2" s="98" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:43" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AR2" s="99" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="82"/>
       <c r="D3" s="82"/>
-      <c r="E3" s="9"/>
+      <c r="E3" s="82"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="11" t="s">
+      <c r="N3" s="9"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="104" t="s">
+      <c r="R3" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="105"/>
       <c r="S3" s="105"/>
       <c r="T3" s="105"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="117" t="s">
+      <c r="U3" s="105"/>
+      <c r="V3" s="106"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="117" t="s">
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="123"/>
+      <c r="AB3" s="118"/>
       <c r="AC3" s="123"/>
       <c r="AD3" s="123"/>
       <c r="AE3" s="123"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="107" t="s">
+      <c r="AF3" s="123"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="108"/>
-      <c r="AI3" s="109" t="s">
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="AJ3" s="110"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="89"/>
+      <c r="AK3" s="110"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="40"/>
       <c r="AN3" s="89"/>
       <c r="AO3" s="89"/>
-      <c r="AP3" s="100"/>
-      <c r="AQ3" s="101"/>
-    </row>
-    <row r="4" spans="1:43" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AP3" s="89"/>
+      <c r="AQ3" s="100"/>
+      <c r="AR3" s="101"/>
+    </row>
+    <row r="4" spans="1:44" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="83"/>
       <c r="D4" s="83"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="15"/>
+      <c r="N4" s="14"/>
       <c r="O4" s="15"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="26"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="25"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="90"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="48"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="91"/>
+      <c r="Z4" s="90"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="47"/>
       <c r="AD4" s="48"/>
       <c r="AE4" s="48"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="42"/>
-      <c r="AH4" s="43"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="42"/>
       <c r="AI4" s="43"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="89"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="50"/>
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="52"/>
       <c r="AN4" s="89"/>
       <c r="AO4" s="89"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="103"/>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AJ5" s="55"/>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AI9" s="29" t="s">
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="102"/>
+      <c r="AR4" s="103"/>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AK5" s="55"/>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AJ9" s="29" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AG2:AJ2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="AB3:AE3"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AC3:AF3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="participant" display="Participant / Manufacturer" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B1" r:id="rId2" location="brand" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C1" r:id="rId3" location="basic_model_number" display="Basic Model Designation" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D1" r:id="rId4" location="individual_model_number" display="Manufacturer (individual) model number" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E1" r:id="rId5" location="category" display="Equipment Category of rated pump" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F1" r:id="rId6" location="configuration" display="Configuration of rated pump" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G1" r:id="rId7" location="diameter" display="&quot;Full&quot; Impeller Diameter" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H1" r:id="rId8" location="section" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I1" r:id="rId9" location="stages" display="For RSV and ST Pumps # of Stages" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J1" r:id="rId10" location="speed" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K1" r:id="rId11" location="bowl_diameter" display="Pump Bowl Diameter if applicable" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="M1" r:id="rId12" location="motor_regulated" display="Is Motor Regulated under 10 CFR?" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N1" r:id="rId13" location="nominal_efficiency" display="If regulated under 10 CFR 431.25 - Nominal Motor Efficiency" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O1" r:id="rId14" location="motor_power_rated_3" display="For section III, the Motor power used for default losses or for section IV, V, VI, VII, the   rated motor horsepower" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="P1" r:id="rId15" location="bep120" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q1" r:id="rId16" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="R1" r:id="rId17" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="S1" r:id="rId18" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="T1" r:id="rId19" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="U1" r:id="rId20" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="V1" r:id="rId21" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="W1" r:id="rId22" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="X1" r:id="rId23" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="Y1" r:id="rId24" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="Z1" r:id="rId25" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="AA1" r:id="rId26" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="AB1" r:id="rId27" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="AC1" r:id="rId28" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="AD1" r:id="rId29" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="AE1" r:id="rId30" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="AG1" r:id="rId31" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="AH1" r:id="rId32" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="AI1" r:id="rId33" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="AJ1" r:id="rId34" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="AF1" r:id="rId35" location="pei_entry" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="AK1" r:id="rId36" location="lab" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L1" r:id="rId37" location="motor_type" xr:uid="{4D5CAC20-CAA8-46F0-8392-491D000D55B1}"/>
+    <hyperlink ref="F1" r:id="rId5" location="category" display="Equipment Category of rated pump" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G1" r:id="rId6" location="configuration" display="Configuration of rated pump" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H1" r:id="rId7" location="diameter" display="&quot;Full&quot; Impeller Diameter" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I1" r:id="rId8" location="section" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J1" r:id="rId9" location="stages" display="For RSV and ST Pumps # of Stages" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K1" r:id="rId10" location="speed" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="L1" r:id="rId11" location="bowl_diameter" display="Pump Bowl Diameter if applicable" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N1" r:id="rId12" location="motor_regulated" display="Is Motor Regulated under 10 CFR?" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O1" r:id="rId13" location="nominal_efficiency" display="If regulated under 10 CFR 431.25 - Nominal Motor Efficiency" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P1" r:id="rId14" location="motor_power_rated_3" display="For section III, the Motor power used for default losses or for section IV, V, VI, VII, the   rated motor horsepower" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="Q1" r:id="rId15" location="bep120" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="R1" r:id="rId16" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="S1" r:id="rId17" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="T1" r:id="rId18" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="U1" r:id="rId19" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="V1" r:id="rId20" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="W1" r:id="rId21" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="X1" r:id="rId22" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="Y1" r:id="rId23" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="Z1" r:id="rId24" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="AA1" r:id="rId25" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="AB1" r:id="rId26" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="AC1" r:id="rId27" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="AD1" r:id="rId28" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="AE1" r:id="rId29" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="AF1" r:id="rId30" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="AH1" r:id="rId31" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="AI1" r:id="rId32" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="AJ1" r:id="rId33" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="AK1" r:id="rId34" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="AG1" r:id="rId35" location="pei_entry" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="AL1" r:id="rId36" location="lab" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M1" r:id="rId37" location="motor_type" xr:uid="{4D5CAC20-CAA8-46F0-8392-491D000D55B1}"/>
+    <hyperlink ref="E1" r:id="rId38" location="alternative_part_number" xr:uid="{C17D1C91-B9F2-465B-AD81-9F003F584224}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -2138,37 +2185,37 @@
           <x14:formula1>
             <xm:f>Choicelists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F578</xm:sqref>
+          <xm:sqref>G5:G578</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{368E6EB0-807F-47B8-8B52-718C2947B13F}">
           <x14:formula1>
             <xm:f>Choicelists!$A$13:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E100</xm:sqref>
+          <xm:sqref>F5:F100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B7E52111-AF20-4B53-BB3A-8C79B5EDE179}">
           <x14:formula1>
             <xm:f>Choicelists!$A$8:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>L5:L100</xm:sqref>
+          <xm:sqref>M5:M100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A2EB3AB-3C0E-4EFE-A2CE-0E8FE297782A}">
           <x14:formula1>
             <xm:f>Choicelists!$F$7:$F$11</xm:f>
           </x14:formula1>
-          <xm:sqref>H5:H100</xm:sqref>
+          <xm:sqref>I5:I100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76C8E1BD-19F5-40E5-A9C6-C5BC73DF21EA}">
           <x14:formula1>
             <xm:f>Choicelists!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>J5:J100</xm:sqref>
+          <xm:sqref>K5:K100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E806004C-5E21-4EF6-B9FA-83D8A9B80A19}">
           <x14:formula1>
             <xm:f>Choicelists!$F$15:$F$16</xm:f>
           </x14:formula1>
-          <xm:sqref>P5:P100</xm:sqref>
+          <xm:sqref>Q5:Q100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\dev\hi-er\apps\site\routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\orig\hi-er\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C50805C-8CF5-42C9-80F6-4CA496FD8DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB1220-E02E-4ADA-AABB-07B2EA4C5E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="3936" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -1255,6 +1255,9 @@
     <xf numFmtId="2" fontId="0" fillId="12" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,9 +1317,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="89">
@@ -1932,7 +1932,7 @@
       <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="124" t="s">
+      <c r="E2" s="104" t="s">
         <v>81</v>
       </c>
       <c r="F2" s="80" t="s">
@@ -1971,26 +1971,26 @@
       <c r="W2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="114" t="s">
+      <c r="X2" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
-      <c r="AA2" s="115"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="120" t="s">
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="AD2" s="121"/>
-      <c r="AE2" s="121"/>
-      <c r="AF2" s="122"/>
+      <c r="AD2" s="122"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="123"/>
       <c r="AG2" s="33"/>
-      <c r="AH2" s="111" t="s">
+      <c r="AH2" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="AI2" s="112"/>
-      <c r="AJ2" s="112"/>
-      <c r="AK2" s="113"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="113"/>
+      <c r="AK2" s="114"/>
       <c r="AL2" s="34" t="s">
         <v>38</v>
       </c>
@@ -2033,36 +2033,36 @@
       <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="104" t="s">
+      <c r="R3" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="105"/>
-      <c r="T3" s="105"/>
-      <c r="U3" s="105"/>
-      <c r="V3" s="106"/>
+      <c r="S3" s="106"/>
+      <c r="T3" s="106"/>
+      <c r="U3" s="106"/>
+      <c r="V3" s="107"/>
       <c r="W3" s="36"/>
       <c r="X3" s="37"/>
-      <c r="Y3" s="117" t="s">
+      <c r="Y3" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="117" t="s">
+      <c r="Z3" s="120"/>
+      <c r="AA3" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="123"/>
-      <c r="AD3" s="123"/>
-      <c r="AE3" s="123"/>
-      <c r="AF3" s="123"/>
+      <c r="AB3" s="119"/>
+      <c r="AC3" s="124"/>
+      <c r="AD3" s="124"/>
+      <c r="AE3" s="124"/>
+      <c r="AF3" s="124"/>
       <c r="AG3" s="38"/>
-      <c r="AH3" s="107" t="s">
+      <c r="AH3" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="AI3" s="108"/>
-      <c r="AJ3" s="109" t="s">
+      <c r="AI3" s="109"/>
+      <c r="AJ3" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="AK3" s="110"/>
+      <c r="AK3" s="111"/>
       <c r="AL3" s="39"/>
       <c r="AM3" s="40"/>
       <c r="AN3" s="89"/>
@@ -2369,7 +2369,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="85">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2377,7 +2377,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="86">
-        <v>45391</v>
+        <v>46108</v>
       </c>
     </row>
   </sheetData>

--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\hi-er\routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\orig\hi-er\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CA52A0-ED1B-4F58-BF2C-7E3078C0BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB1220-E02E-4ADA-AABB-07B2EA4C5E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4716" yWindow="3648" windowWidth="19860" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Nominal Speed</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>Annual Cost Savings</t>
+  </si>
+  <si>
+    <t>(Optional) Alternative number that the participant puts on the nameplate that they would like to be searchable in the HI database.</t>
+  </si>
+  <si>
+    <t>Alternative Part Number</t>
   </si>
 </sst>
 </file>
@@ -300,7 +306,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,8 +368,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,8 +449,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDEEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -852,6 +871,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -944,7 +978,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1220,6 +1254,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="12" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1708,46 +1745,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AR9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.59765625" customWidth="1"/>
     <col min="3" max="3" width="20.09765625" style="84" customWidth="1"/>
     <col min="4" max="4" width="22.5" style="84" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="21"/>
-    <col min="8" max="8" width="13.3984375" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" customWidth="1"/>
-    <col min="12" max="12" width="34.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.3984375" customWidth="1"/>
-    <col min="15" max="15" width="18.3984375" customWidth="1"/>
-    <col min="16" max="16" width="14.8984375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11" style="28" customWidth="1"/>
-    <col min="18" max="19" width="11" style="29" customWidth="1"/>
-    <col min="20" max="20" width="11" style="29"/>
-    <col min="21" max="21" width="11" style="30" customWidth="1"/>
-    <col min="22" max="22" width="11" style="29"/>
-    <col min="23" max="23" width="11" style="28"/>
-    <col min="24" max="24" width="11" style="54"/>
-    <col min="25" max="25" width="11" style="53"/>
-    <col min="26" max="26" width="11" style="29"/>
-    <col min="27" max="27" width="11" style="30"/>
-    <col min="28" max="28" width="11" style="28"/>
-    <col min="29" max="30" width="11" style="29"/>
-    <col min="31" max="31" width="11" style="30"/>
-    <col min="32" max="32" width="11" style="28"/>
-    <col min="33" max="33" width="11" style="28" customWidth="1"/>
-    <col min="34" max="35" width="11" style="29" customWidth="1"/>
-    <col min="36" max="36" width="11" style="30" customWidth="1"/>
-    <col min="37" max="37" width="21.3984375" style="56" customWidth="1"/>
-    <col min="38" max="41" width="18.59765625" style="56" customWidth="1"/>
-    <col min="42" max="42" width="11" style="94"/>
-    <col min="43" max="43" width="11" style="95"/>
+    <col min="5" max="5" width="22.5" style="84" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="21"/>
+    <col min="9" max="9" width="13.3984375" customWidth="1"/>
+    <col min="11" max="11" width="11.59765625" customWidth="1"/>
+    <col min="13" max="13" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.3984375" customWidth="1"/>
+    <col min="16" max="16" width="18.3984375" customWidth="1"/>
+    <col min="17" max="17" width="14.8984375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11" style="28" customWidth="1"/>
+    <col min="19" max="20" width="11" style="29" customWidth="1"/>
+    <col min="21" max="21" width="11" style="29"/>
+    <col min="22" max="22" width="11" style="30" customWidth="1"/>
+    <col min="23" max="23" width="11" style="29"/>
+    <col min="24" max="24" width="11" style="28"/>
+    <col min="25" max="25" width="11" style="54"/>
+    <col min="26" max="26" width="11" style="53"/>
+    <col min="27" max="27" width="11" style="29"/>
+    <col min="28" max="28" width="11" style="30"/>
+    <col min="29" max="29" width="11" style="28"/>
+    <col min="30" max="31" width="11" style="29"/>
+    <col min="32" max="32" width="11" style="30"/>
+    <col min="33" max="33" width="11" style="28"/>
+    <col min="34" max="34" width="11" style="28" customWidth="1"/>
+    <col min="35" max="36" width="11" style="29" customWidth="1"/>
+    <col min="37" max="37" width="11" style="30" customWidth="1"/>
+    <col min="38" max="38" width="21.3984375" style="56" customWidth="1"/>
+    <col min="39" max="42" width="18.59765625" style="56" customWidth="1"/>
+    <col min="43" max="43" width="11" style="94"/>
+    <col min="44" max="44" width="11" style="95"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>49</v>
       </c>
@@ -1760,125 +1798,128 @@
       <c r="D1" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="81" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="I1" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="J1" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="K1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="L1" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="M1" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="N1" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="59" t="s">
+      <c r="O1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="P1" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="62" t="s">
+      <c r="Q1" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="63" t="s">
+      <c r="R1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="S1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="64" t="s">
+      <c r="T1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="65" t="s">
+      <c r="U1" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="66" t="s">
+      <c r="V1" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="67" t="s">
+      <c r="W1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="68" t="s">
+      <c r="X1" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="69" t="s">
+      <c r="Y1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="70" t="s">
+      <c r="Z1" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="70" t="s">
+      <c r="AA1" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="71" t="s">
+      <c r="AB1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="72" t="s">
+      <c r="AC1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="AC1" s="73" t="s">
+      <c r="AD1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="73" t="s">
+      <c r="AE1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="74" t="s">
+      <c r="AF1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="78" t="s">
+      <c r="AG1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AG1" s="75" t="s">
+      <c r="AH1" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="AH1" s="76" t="s">
+      <c r="AI1" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="76" t="s">
+      <c r="AJ1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="77" t="s">
+      <c r="AK1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="79" t="s">
+      <c r="AL1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="31" t="s">
+      <c r="AM1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="AM1" s="87" t="s">
+      <c r="AN1" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="87" t="s">
+      <c r="AO1" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="AO1" s="87" t="s">
+      <c r="AP1" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="AP1" s="96" t="s">
+      <c r="AQ1" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="AQ1" s="97" t="s">
+      <c r="AR1" s="97" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="7" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>64</v>
       </c>
@@ -1891,69 +1932,69 @@
       <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="104" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="18"/>
+      <c r="I2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="23"/>
+      <c r="R2" s="22"/>
       <c r="S2" s="23"/>
       <c r="T2" s="23"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="32" t="s">
+      <c r="U2" s="23"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="114" t="s">
+      <c r="X2" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="115"/>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
       <c r="AA2" s="116"/>
-      <c r="AB2" s="120" t="s">
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" s="121"/>
-      <c r="AD2" s="121"/>
+      <c r="AD2" s="122"/>
       <c r="AE2" s="122"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="111" t="s">
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="AH2" s="112"/>
-      <c r="AI2" s="112"/>
+      <c r="AI2" s="113"/>
       <c r="AJ2" s="113"/>
-      <c r="AK2" s="34" t="s">
+      <c r="AK2" s="114"/>
+      <c r="AL2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AL2" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AM2" s="88" t="s">
+      <c r="AM2" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AN2" s="88" t="s">
@@ -1962,173 +2003,179 @@
       <c r="AO2" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="AP2" s="98" t="s">
+      <c r="AP2" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="AQ2" s="99" t="s">
+      <c r="AQ2" s="98" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:43" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AR2" s="99" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="82"/>
       <c r="D3" s="82"/>
-      <c r="E3" s="9"/>
+      <c r="E3" s="82"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="11" t="s">
+      <c r="N3" s="9"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="104" t="s">
+      <c r="R3" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-      <c r="T3" s="105"/>
+      <c r="S3" s="106"/>
+      <c r="T3" s="106"/>
       <c r="U3" s="106"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="117" t="s">
+      <c r="V3" s="107"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="117" t="s">
+      <c r="Z3" s="120"/>
+      <c r="AA3" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="123"/>
-      <c r="AD3" s="123"/>
-      <c r="AE3" s="123"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="107" t="s">
+      <c r="AB3" s="119"/>
+      <c r="AC3" s="124"/>
+      <c r="AD3" s="124"/>
+      <c r="AE3" s="124"/>
+      <c r="AF3" s="124"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="108"/>
-      <c r="AI3" s="109" t="s">
+      <c r="AI3" s="109"/>
+      <c r="AJ3" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="AJ3" s="110"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="89"/>
+      <c r="AK3" s="111"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="40"/>
       <c r="AN3" s="89"/>
       <c r="AO3" s="89"/>
-      <c r="AP3" s="100"/>
-      <c r="AQ3" s="101"/>
-    </row>
-    <row r="4" spans="1:43" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AP3" s="89"/>
+      <c r="AQ3" s="100"/>
+      <c r="AR3" s="101"/>
+    </row>
+    <row r="4" spans="1:44" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="83"/>
       <c r="D4" s="83"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="15"/>
+      <c r="N4" s="14"/>
       <c r="O4" s="15"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="26"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="25"/>
       <c r="S4" s="26"/>
       <c r="T4" s="26"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="90"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="48"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="91"/>
+      <c r="Z4" s="90"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="47"/>
       <c r="AD4" s="48"/>
       <c r="AE4" s="48"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="42"/>
-      <c r="AH4" s="43"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="42"/>
       <c r="AI4" s="43"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="52"/>
-      <c r="AM4" s="89"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="50"/>
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="52"/>
       <c r="AN4" s="89"/>
       <c r="AO4" s="89"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="103"/>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AJ5" s="55"/>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AI9" s="29" t="s">
+      <c r="AP4" s="89"/>
+      <c r="AQ4" s="102"/>
+      <c r="AR4" s="103"/>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AK5" s="55"/>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AJ9" s="29" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AG2:AJ2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="AB3:AE3"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AC3:AF3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="participant" display="Participant / Manufacturer" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B1" r:id="rId2" location="brand" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C1" r:id="rId3" location="basic_model_number" display="Basic Model Designation" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D1" r:id="rId4" location="individual_model_number" display="Manufacturer (individual) model number" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E1" r:id="rId5" location="category" display="Equipment Category of rated pump" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F1" r:id="rId6" location="configuration" display="Configuration of rated pump" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G1" r:id="rId7" location="diameter" display="&quot;Full&quot; Impeller Diameter" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H1" r:id="rId8" location="section" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I1" r:id="rId9" location="stages" display="For RSV and ST Pumps # of Stages" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J1" r:id="rId10" location="speed" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K1" r:id="rId11" location="bowl_diameter" display="Pump Bowl Diameter if applicable" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="M1" r:id="rId12" location="motor_regulated" display="Is Motor Regulated under 10 CFR?" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N1" r:id="rId13" location="nominal_efficiency" display="If regulated under 10 CFR 431.25 - Nominal Motor Efficiency" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O1" r:id="rId14" location="motor_power_rated_3" display="For section III, the Motor power used for default losses or for section IV, V, VI, VII, the   rated motor horsepower" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="P1" r:id="rId15" location="bep120" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q1" r:id="rId16" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="R1" r:id="rId17" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="S1" r:id="rId18" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="T1" r:id="rId19" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="U1" r:id="rId20" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="V1" r:id="rId21" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="W1" r:id="rId22" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="X1" r:id="rId23" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="Y1" r:id="rId24" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="Z1" r:id="rId25" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="AA1" r:id="rId26" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="AB1" r:id="rId27" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="AC1" r:id="rId28" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="AD1" r:id="rId29" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="AE1" r:id="rId30" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="AG1" r:id="rId31" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="AH1" r:id="rId32" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="AI1" r:id="rId33" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="AJ1" r:id="rId34" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="AF1" r:id="rId35" location="pei_entry" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="AK1" r:id="rId36" location="lab" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L1" r:id="rId37" location="motor_type" xr:uid="{4D5CAC20-CAA8-46F0-8392-491D000D55B1}"/>
+    <hyperlink ref="F1" r:id="rId5" location="category" display="Equipment Category of rated pump" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G1" r:id="rId6" location="configuration" display="Configuration of rated pump" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H1" r:id="rId7" location="diameter" display="&quot;Full&quot; Impeller Diameter" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I1" r:id="rId8" location="section" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J1" r:id="rId9" location="stages" display="For RSV and ST Pumps # of Stages" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K1" r:id="rId10" location="speed" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="L1" r:id="rId11" location="bowl_diameter" display="Pump Bowl Diameter if applicable" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N1" r:id="rId12" location="motor_regulated" display="Is Motor Regulated under 10 CFR?" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O1" r:id="rId13" location="nominal_efficiency" display="If regulated under 10 CFR 431.25 - Nominal Motor Efficiency" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P1" r:id="rId14" location="motor_power_rated_3" display="For section III, the Motor power used for default losses or for section IV, V, VI, VII, the   rated motor horsepower" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="Q1" r:id="rId15" location="bep120" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="R1" r:id="rId16" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="S1" r:id="rId17" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="T1" r:id="rId18" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="U1" r:id="rId19" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="V1" r:id="rId20" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="W1" r:id="rId21" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="X1" r:id="rId22" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="Y1" r:id="rId23" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="Z1" r:id="rId24" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="AA1" r:id="rId25" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="AB1" r:id="rId26" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="AC1" r:id="rId27" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="AD1" r:id="rId28" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="AE1" r:id="rId29" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="AF1" r:id="rId30" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="AH1" r:id="rId31" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="AI1" r:id="rId32" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="AJ1" r:id="rId33" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="AK1" r:id="rId34" location="rep_nominal_speed" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="AG1" r:id="rId35" location="pei_entry" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="AL1" r:id="rId36" location="lab" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M1" r:id="rId37" location="motor_type" xr:uid="{4D5CAC20-CAA8-46F0-8392-491D000D55B1}"/>
+    <hyperlink ref="E1" r:id="rId38" location="alternative_part_number" xr:uid="{C17D1C91-B9F2-465B-AD81-9F003F584224}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -2138,37 +2185,37 @@
           <x14:formula1>
             <xm:f>Choicelists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F578</xm:sqref>
+          <xm:sqref>G5:G578</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{368E6EB0-807F-47B8-8B52-718C2947B13F}">
           <x14:formula1>
             <xm:f>Choicelists!$A$13:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E100</xm:sqref>
+          <xm:sqref>F5:F100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B7E52111-AF20-4B53-BB3A-8C79B5EDE179}">
           <x14:formula1>
             <xm:f>Choicelists!$A$8:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>L5:L100</xm:sqref>
+          <xm:sqref>M5:M100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A2EB3AB-3C0E-4EFE-A2CE-0E8FE297782A}">
           <x14:formula1>
             <xm:f>Choicelists!$F$7:$F$11</xm:f>
           </x14:formula1>
-          <xm:sqref>H5:H100</xm:sqref>
+          <xm:sqref>I5:I100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76C8E1BD-19F5-40E5-A9C6-C5BC73DF21EA}">
           <x14:formula1>
             <xm:f>Choicelists!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>J5:J100</xm:sqref>
+          <xm:sqref>K5:K100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E806004C-5E21-4EF6-B9FA-83D8A9B80A19}">
           <x14:formula1>
             <xm:f>Choicelists!$F$15:$F$16</xm:f>
           </x14:formula1>
-          <xm:sqref>P5:P100</xm:sqref>
+          <xm:sqref>Q5:Q100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2322,7 +2369,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="85">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2330,7 +2377,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="86">
-        <v>45391</v>
+        <v>46108</v>
       </c>
     </row>
   </sheetData>

--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\orig\hi-er\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB1220-E02E-4ADA-AABB-07B2EA4C5E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECB4B8C-9410-4198-86E1-937337A1515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2328" yWindow="3216" windowWidth="24396" windowHeight="12012" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
   <si>
     <t>Nominal Speed</t>
   </si>
@@ -297,6 +297,10 @@
   </si>
   <si>
     <t>Alternative Part Number</t>
+  </si>
+  <si>
+    <t>Only enter data here when updating pumps. 
+Otherwise, only applicable on export.</t>
   </si>
 </sst>
 </file>
@@ -2001,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="AO2" s="88" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="AP2" s="88" t="s">
         <v>20</v>
@@ -2369,7 +2373,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="85">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2377,7 +2381,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="86">
-        <v>46108</v>
+        <v>46209</v>
       </c>
     </row>
   </sheetData>

--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\orig\hi-er\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECB4B8C-9410-4198-86E1-937337A1515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54059514-6307-4746-96CD-5F3A192DA15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2328" yWindow="3216" windowWidth="24396" windowHeight="12012" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9636" yWindow="2292" windowWidth="20892" windowHeight="12012" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="87">
   <si>
     <t>Nominal Speed</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Not displayed on the label</t>
   </si>
   <si>
-    <t>Displayed on the label</t>
-  </si>
-  <si>
     <t>Equipment Category
 of rated pump</t>
   </si>
@@ -299,8 +296,49 @@
     <t>Alternative Part Number</t>
   </si>
   <si>
-    <t>Only enter data here when updating pumps. 
+    <t>Revision Note</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Not displayed on the label
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do not change for an update</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Displayed on the label
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do not change for an update</t>
+    </r>
+  </si>
+  <si>
+    <t>Enter the Rating ID when updating pumps. 
 Otherwise, only applicable on export.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Enter data here when updating pumps.
+Otherwise, not applicable </t>
   </si>
 </sst>
 </file>
@@ -460,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -890,6 +928,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -982,7 +1035,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1260,6 +1313,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1749,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR9"/>
+  <dimension ref="A1:AS9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.8984375" style="1" customWidth="1"/>
@@ -1787,9 +1849,10 @@
     <col min="39" max="42" width="18.59765625" style="56" customWidth="1"/>
     <col min="43" max="43" width="11" style="94"/>
     <col min="44" max="44" width="11" style="95"/>
+    <col min="45" max="45" width="21.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:45" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>49</v>
       </c>
@@ -1803,10 +1866,10 @@
         <v>51</v>
       </c>
       <c r="E1" s="81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G1" s="59" t="s">
         <v>52</v>
@@ -1917,27 +1980,30 @@
         <v>59</v>
       </c>
       <c r="AQ1" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR1" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="AR1" s="97" t="s">
-        <v>80</v>
+      <c r="AS1" s="107" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:45" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E2" s="104" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="80" t="s">
         <v>41</v>
@@ -1975,26 +2041,26 @@
       <c r="W2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="115" t="s">
+      <c r="X2" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="121" t="s">
+      <c r="Y2" s="119"/>
+      <c r="Z2" s="119"/>
+      <c r="AA2" s="119"/>
+      <c r="AB2" s="120"/>
+      <c r="AC2" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="123"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="126"/>
       <c r="AG2" s="33"/>
-      <c r="AH2" s="112" t="s">
+      <c r="AH2" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="113"/>
-      <c r="AK2" s="114"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="117"/>
       <c r="AL2" s="34" t="s">
         <v>38</v>
       </c>
@@ -2005,7 +2071,7 @@
         <v>20</v>
       </c>
       <c r="AO2" s="88" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AP2" s="88" t="s">
         <v>20</v>
@@ -2016,8 +2082,11 @@
       <c r="AR2" s="99" t="s">
         <v>20</v>
       </c>
+      <c r="AS2" s="88" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:45" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="82"/>
@@ -2037,36 +2106,36 @@
       <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="105" t="s">
+      <c r="R3" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="107"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="110"/>
       <c r="W3" s="36"/>
       <c r="X3" s="37"/>
-      <c r="Y3" s="118" t="s">
+      <c r="Y3" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="120"/>
-      <c r="AA3" s="118" t="s">
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="124"/>
-      <c r="AE3" s="124"/>
-      <c r="AF3" s="124"/>
+      <c r="AB3" s="122"/>
+      <c r="AC3" s="127"/>
+      <c r="AD3" s="127"/>
+      <c r="AE3" s="127"/>
+      <c r="AF3" s="127"/>
       <c r="AG3" s="38"/>
-      <c r="AH3" s="108" t="s">
+      <c r="AH3" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="AI3" s="109"/>
-      <c r="AJ3" s="110" t="s">
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="AK3" s="111"/>
+      <c r="AK3" s="114"/>
       <c r="AL3" s="39"/>
       <c r="AM3" s="40"/>
       <c r="AN3" s="89"/>
@@ -2074,8 +2143,9 @@
       <c r="AP3" s="89"/>
       <c r="AQ3" s="100"/>
       <c r="AR3" s="101"/>
+      <c r="AS3" s="105"/>
     </row>
-    <row r="4" spans="1:44" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:45" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="83"/>
@@ -2120,11 +2190,12 @@
       <c r="AP4" s="89"/>
       <c r="AQ4" s="102"/>
       <c r="AR4" s="103"/>
+      <c r="AS4" s="106"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
       <c r="AK5" s="55"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
       <c r="AJ9" s="29" t="s">
         <v>28</v>
       </c>
@@ -2271,7 +2342,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F6" s="92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2284,7 +2355,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -2292,7 +2363,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2300,7 +2371,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -2313,17 +2384,17 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="92" t="s">
         <v>22</v>
@@ -2331,23 +2402,23 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/routes/er_pump_listings.xlsx
+++ b/routes/er_pump_listings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\orig\hi-er\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB1220-E02E-4ADA-AABB-07B2EA4C5E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54059514-6307-4746-96CD-5F3A192DA15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9636" yWindow="2292" windowWidth="20892" windowHeight="12012" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import-Export Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="87">
   <si>
     <t>Nominal Speed</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Not displayed on the label</t>
   </si>
   <si>
-    <t>Displayed on the label</t>
-  </si>
-  <si>
     <t>Equipment Category
 of rated pump</t>
   </si>
@@ -297,6 +294,51 @@
   </si>
   <si>
     <t>Alternative Part Number</t>
+  </si>
+  <si>
+    <t>Revision Note</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Not displayed on the label
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do not change for an update</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Displayed on the label
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do not change for an update</t>
+    </r>
+  </si>
+  <si>
+    <t>Enter the Rating ID when updating pumps. 
+Otherwise, only applicable on export.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Enter data here when updating pumps.
+Otherwise, not applicable </t>
   </si>
 </sst>
 </file>
@@ -456,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -886,6 +928,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -978,7 +1035,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1256,6 +1313,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1745,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR9"/>
+  <dimension ref="A1:AS9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.8984375" style="1" customWidth="1"/>
@@ -1783,9 +1849,10 @@
     <col min="39" max="42" width="18.59765625" style="56" customWidth="1"/>
     <col min="43" max="43" width="11" style="94"/>
     <col min="44" max="44" width="11" style="95"/>
+    <col min="45" max="45" width="21.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:45" s="3" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>49</v>
       </c>
@@ -1799,10 +1866,10 @@
         <v>51</v>
       </c>
       <c r="E1" s="81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G1" s="59" t="s">
         <v>52</v>
@@ -1913,27 +1980,30 @@
         <v>59</v>
       </c>
       <c r="AQ1" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR1" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="AR1" s="97" t="s">
-        <v>80</v>
+      <c r="AS1" s="107" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:45" s="7" customFormat="1" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E2" s="104" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="80" t="s">
         <v>41</v>
@@ -1971,26 +2041,26 @@
       <c r="W2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="115" t="s">
+      <c r="X2" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="121" t="s">
+      <c r="Y2" s="119"/>
+      <c r="Z2" s="119"/>
+      <c r="AA2" s="119"/>
+      <c r="AB2" s="120"/>
+      <c r="AC2" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="123"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="126"/>
       <c r="AG2" s="33"/>
-      <c r="AH2" s="112" t="s">
+      <c r="AH2" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="113"/>
-      <c r="AK2" s="114"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="117"/>
       <c r="AL2" s="34" t="s">
         <v>38</v>
       </c>
@@ -2001,7 +2071,7 @@
         <v>20</v>
       </c>
       <c r="AO2" s="88" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AP2" s="88" t="s">
         <v>20</v>
@@ -2012,8 +2082,11 @@
       <c r="AR2" s="99" t="s">
         <v>20</v>
       </c>
+      <c r="AS2" s="88" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:45" s="12" customFormat="1" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="82"/>
@@ -2033,36 +2106,36 @@
       <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="105" t="s">
+      <c r="R3" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="107"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="110"/>
       <c r="W3" s="36"/>
       <c r="X3" s="37"/>
-      <c r="Y3" s="118" t="s">
+      <c r="Y3" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="120"/>
-      <c r="AA3" s="118" t="s">
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="124"/>
-      <c r="AE3" s="124"/>
-      <c r="AF3" s="124"/>
+      <c r="AB3" s="122"/>
+      <c r="AC3" s="127"/>
+      <c r="AD3" s="127"/>
+      <c r="AE3" s="127"/>
+      <c r="AF3" s="127"/>
       <c r="AG3" s="38"/>
-      <c r="AH3" s="108" t="s">
+      <c r="AH3" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="AI3" s="109"/>
-      <c r="AJ3" s="110" t="s">
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="AK3" s="111"/>
+      <c r="AK3" s="114"/>
       <c r="AL3" s="39"/>
       <c r="AM3" s="40"/>
       <c r="AN3" s="89"/>
@@ -2070,8 +2143,9 @@
       <c r="AP3" s="89"/>
       <c r="AQ3" s="100"/>
       <c r="AR3" s="101"/>
+      <c r="AS3" s="105"/>
     </row>
-    <row r="4" spans="1:44" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:45" s="17" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="83"/>
@@ -2116,11 +2190,12 @@
       <c r="AP4" s="89"/>
       <c r="AQ4" s="102"/>
       <c r="AR4" s="103"/>
+      <c r="AS4" s="106"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
       <c r="AK5" s="55"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
       <c r="AJ9" s="29" t="s">
         <v>28</v>
       </c>
@@ -2267,7 +2342,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F6" s="92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2280,7 +2355,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -2288,7 +2363,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2296,7 +2371,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -2309,17 +2384,17 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="92" t="s">
         <v>22</v>
@@ -2327,23 +2402,23 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2444,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="85">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2377,7 +2452,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="86">
-        <v>46108</v>
+        <v>46209</v>
       </c>
     </row>
   </sheetData>
